--- a/table/output.heta.xlsx
+++ b/table/output.heta.xlsx
@@ -490,13 +490,13 @@
         <v>0.10.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-03-19T15:46:09.034Z</v>
+        <v>2026-03-19T17:48:11.232Z</v>
       </c>
       <c r="R2" t="str">
         <v>faah-inhibitor</v>
       </c>
       <c r="S2" t="str">
-        <v>1.0.2</v>
+        <v>1.0.3</v>
       </c>
       <c r="T2" t="str">
         <v>Table</v>

--- a/table/output.heta.xlsx
+++ b/table/output.heta.xlsx
@@ -490,7 +490,7 @@
         <v>0.10.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-03-19T17:48:11.232Z</v>
+        <v>2026-03-19T17:53:47.142Z</v>
       </c>
       <c r="R2" t="str">
         <v>faah-inhibitor</v>

--- a/table/output.heta.xlsx
+++ b/table/output.heta.xlsx
@@ -490,7 +490,7 @@
         <v>0.10.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-03-19T17:53:47.142Z</v>
+        <v>2026-03-19T17:59:58.916Z</v>
       </c>
       <c r="R2" t="str">
         <v>faah-inhibitor</v>
